--- a/data/location-labels.xlsx
+++ b/data/location-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,367 +421,27 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="E2" t="str">
-        <v>C060103</v>
+        <v>B070199</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>C</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="str">
-        <v>C060104</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>C</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4" t="str">
-        <v>C060105</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>C</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5" t="str">
-        <v>C060106</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>C</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C060107</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>C</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7" t="str">
-        <v>C060108</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>C</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="str">
-        <v>C060109</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>C</v>
-      </c>
-      <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9" t="str">
-        <v>C060110</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>C</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="str">
-        <v>C060101</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>C</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="str">
-        <v>C060102</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>C</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="str">
-        <v>C060103</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>C</v>
-      </c>
-      <c r="B13">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13" t="str">
-        <v>C060104</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>C</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
-      </c>
-      <c r="E14" t="str">
-        <v>C060105</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>C</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
-      <c r="E15" t="str">
-        <v>C060106</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>C</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>7</v>
-      </c>
-      <c r="E16" t="str">
-        <v>C060107</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>C</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-      <c r="E17" t="str">
-        <v>C060108</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>C</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>9</v>
-      </c>
-      <c r="E18" t="str">
-        <v>C060109</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>C</v>
-      </c>
-      <c r="B19">
-        <v>6</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
-      <c r="E19" t="str">
-        <v>C060110</v>
-      </c>
-      <c r="F19">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>